--- a/july 2026/GT_JULY_26/02-07-2026/Umair.xlsx
+++ b/july 2026/GT_JULY_26/02-07-2026/Umair.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{388542AA-D5C8-41B9-B73C-B93329CC976B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA91D3AD-A5CF-4A1D-A9E7-643B86B77073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="13" r:id="rId1"/>
@@ -3268,7 +3268,7 @@
       <c r="M4" s="239"/>
       <c r="N4" s="253">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="253"/>
       <c r="P4" s="253"/>
@@ -3296,7 +3296,7 @@
       <c r="M5" s="239"/>
       <c r="N5" s="253">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="240"/>
       <c r="P5" s="240"/>
@@ -3597,7 +3597,7 @@
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
@@ -3656,8 +3656,8 @@
         <v>0</v>
       </c>
       <c r="J17" s="117"/>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="K17" s="104">
+        <f t="shared" ref="K17:K22" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
@@ -3716,7 +3716,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="117"/>
-      <c r="K18" s="1">
+      <c r="K18" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3772,7 +3772,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="117"/>
-      <c r="K19" s="1">
+      <c r="K19" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3828,7 +3828,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="117"/>
-      <c r="K20" s="1">
+      <c r="K20" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3884,7 +3884,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="117"/>
-      <c r="K21" s="1">
+      <c r="K21" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3942,29 +3942,29 @@
         <v>392.30000000000007</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="3"/>
         <v>13.730500000000003</v>
       </c>
       <c r="L22" s="120">
-        <f>I22*5%</f>
-        <v>19.615000000000006</v>
+        <f>I22*10%</f>
+        <v>39.230000000000011</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="5"/>
-        <v>358.95450000000005</v>
+        <v>339.33950000000004</v>
       </c>
       <c r="N22" s="118">
         <f t="shared" si="0"/>
-        <v>78.96999000000001</v>
+        <v>74.654690000000016</v>
       </c>
       <c r="O22" s="119">
         <f t="shared" si="6"/>
-        <v>10.948112250000001</v>
+        <v>10.349854750000002</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="1"/>
-        <v>448.87260225000006</v>
+        <v>424.34404475000008</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -4107,23 +4107,23 @@
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>19.615000000000006</v>
+        <v>39.230000000000011</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>358.95450000000005</v>
+        <v>339.33950000000004</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>78.96999000000001</v>
+        <v>74.654690000000016</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>10.948112250000001</v>
+        <v>10.349854750000002</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>448.87260225000006</v>
+        <v>424.34404475000008</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -4194,7 +4194,7 @@
       <c r="O29" s="234"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>19.615000000000006</v>
+        <v>39.230000000000011</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4237,7 +4237,7 @@
       <c r="O31" s="234"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>358.95450000000005</v>
+        <v>339.33950000000004</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>78.96999000000001</v>
+        <v>74.654690000000016</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4284,7 +4284,7 @@
       <c r="O33" s="236"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>437.92449000000005</v>
+        <v>413.99419000000006</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>10.948112250000001</v>
+        <v>10.349854750000002</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -4319,7 +4319,7 @@
       <c r="O35" s="214"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>448.87260225000006</v>
+        <v>424.34404475000008</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4399,7 +4399,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="10" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <pageSetup scale="10" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -4491,7 +4491,7 @@
       <c r="M4" s="239"/>
       <c r="N4" s="253">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="253"/>
       <c r="P4" s="253"/>
@@ -4519,7 +4519,7 @@
       <c r="M5" s="239"/>
       <c r="N5" s="253">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="240"/>
       <c r="P5" s="240"/>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
@@ -4879,8 +4879,8 @@
         <v>0</v>
       </c>
       <c r="J17" s="117"/>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="K17" s="104">
+        <f t="shared" ref="K17:K22" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
@@ -4939,7 +4939,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="117"/>
-      <c r="K18" s="1">
+      <c r="K18" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4995,7 +4995,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="117"/>
-      <c r="K19" s="1">
+      <c r="K19" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5051,7 +5051,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="117"/>
-      <c r="K20" s="1">
+      <c r="K20" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5107,7 +5107,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="117"/>
-      <c r="K21" s="1">
+      <c r="K21" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5165,29 +5165,29 @@
         <v>392.30000000000007</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="3"/>
         <v>13.730500000000003</v>
       </c>
       <c r="L22" s="120">
-        <f>I22*5%</f>
-        <v>19.615000000000006</v>
+        <f>I22*10%</f>
+        <v>39.230000000000011</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="5"/>
-        <v>358.95450000000005</v>
+        <v>339.33950000000004</v>
       </c>
       <c r="N22" s="118">
         <f t="shared" si="0"/>
-        <v>78.96999000000001</v>
+        <v>74.654690000000016</v>
       </c>
       <c r="O22" s="119">
         <f t="shared" si="6"/>
-        <v>10.948112250000001</v>
+        <v>10.349854750000002</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="1"/>
-        <v>448.87260225000006</v>
+        <v>424.34404475000008</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -5330,23 +5330,23 @@
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>19.615000000000006</v>
+        <v>39.230000000000011</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>358.95450000000005</v>
+        <v>339.33950000000004</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>78.96999000000001</v>
+        <v>74.654690000000016</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>10.948112250000001</v>
+        <v>10.349854750000002</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>448.87260225000006</v>
+        <v>424.34404475000008</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -5417,7 +5417,7 @@
       <c r="O29" s="234"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>19.615000000000006</v>
+        <v>39.230000000000011</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5460,7 +5460,7 @@
       <c r="O31" s="234"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>358.95450000000005</v>
+        <v>339.33950000000004</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>78.96999000000001</v>
+        <v>74.654690000000016</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5507,7 +5507,7 @@
       <c r="O33" s="236"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>437.92449000000005</v>
+        <v>413.99419000000006</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>10.948112250000001</v>
+        <v>10.349854750000002</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -5542,7 +5542,7 @@
       <c r="O35" s="214"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>448.87260225000006</v>
+        <v>424.34404475000008</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -5622,7 +5622,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="10" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <pageSetup scale="10" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -5714,7 +5714,7 @@
       <c r="M4" s="239"/>
       <c r="N4" s="253">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="253"/>
       <c r="P4" s="253"/>
@@ -5742,7 +5742,7 @@
       <c r="M5" s="239"/>
       <c r="N5" s="253">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="240"/>
       <c r="P5" s="240"/>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
@@ -6102,8 +6102,8 @@
         <v>0</v>
       </c>
       <c r="J17" s="117"/>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="K17" s="104">
+        <f t="shared" ref="K17:K22" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
@@ -6162,7 +6162,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="117"/>
-      <c r="K18" s="1">
+      <c r="K18" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -6218,7 +6218,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="117"/>
-      <c r="K19" s="1">
+      <c r="K19" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -6274,7 +6274,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="117"/>
-      <c r="K20" s="1">
+      <c r="K20" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -6330,7 +6330,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="117"/>
-      <c r="K21" s="1">
+      <c r="K21" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -6388,29 +6388,29 @@
         <v>392.30000000000007</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="3"/>
         <v>13.730500000000003</v>
       </c>
       <c r="L22" s="120">
-        <f>I22*5%</f>
-        <v>19.615000000000006</v>
+        <f>I22*10%</f>
+        <v>39.230000000000011</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="5"/>
-        <v>358.95450000000005</v>
+        <v>339.33950000000004</v>
       </c>
       <c r="N22" s="118">
         <f t="shared" si="0"/>
-        <v>78.96999000000001</v>
+        <v>74.654690000000016</v>
       </c>
       <c r="O22" s="119">
         <f t="shared" si="6"/>
-        <v>10.948112250000001</v>
+        <v>10.349854750000002</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="1"/>
-        <v>448.87260225000006</v>
+        <v>424.34404475000008</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -6553,23 +6553,23 @@
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>19.615000000000006</v>
+        <v>39.230000000000011</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>358.95450000000005</v>
+        <v>339.33950000000004</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>78.96999000000001</v>
+        <v>74.654690000000016</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>10.948112250000001</v>
+        <v>10.349854750000002</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>448.87260225000006</v>
+        <v>424.34404475000008</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -6640,7 +6640,7 @@
       <c r="O29" s="234"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>19.615000000000006</v>
+        <v>39.230000000000011</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6683,7 +6683,7 @@
       <c r="O31" s="234"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>358.95450000000005</v>
+        <v>339.33950000000004</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>78.96999000000001</v>
+        <v>74.654690000000016</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6730,7 +6730,7 @@
       <c r="O33" s="236"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>437.92449000000005</v>
+        <v>413.99419000000006</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>10.948112250000001</v>
+        <v>10.349854750000002</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -6765,7 +6765,7 @@
       <c r="O35" s="214"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>448.87260225000006</v>
+        <v>424.34404475000008</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6845,7 +6845,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="10" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <pageSetup scale="10" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -6937,7 +6937,7 @@
       <c r="M4" s="239"/>
       <c r="N4" s="253">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="253"/>
       <c r="P4" s="253"/>
@@ -6965,7 +6965,7 @@
       <c r="M5" s="239"/>
       <c r="N5" s="253">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="240"/>
       <c r="P5" s="240"/>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
@@ -7325,8 +7325,8 @@
         <v>0</v>
       </c>
       <c r="J17" s="117"/>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="K17" s="104">
+        <f t="shared" ref="K17:K22" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
@@ -7385,7 +7385,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="117"/>
-      <c r="K18" s="1">
+      <c r="K18" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -7441,7 +7441,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="117"/>
-      <c r="K19" s="1">
+      <c r="K19" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -7497,7 +7497,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="117"/>
-      <c r="K20" s="1">
+      <c r="K20" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -7553,7 +7553,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="117"/>
-      <c r="K21" s="1">
+      <c r="K21" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -7611,29 +7611,29 @@
         <v>1569.2000000000003</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="3"/>
         <v>54.922000000000011</v>
       </c>
       <c r="L22" s="120">
-        <f>I22*5%</f>
-        <v>78.460000000000022</v>
+        <f>I22*10%</f>
+        <v>156.92000000000004</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="5"/>
-        <v>1435.8180000000002</v>
+        <v>1357.3580000000002</v>
       </c>
       <c r="N22" s="118">
         <f t="shared" si="0"/>
-        <v>315.87996000000004</v>
+        <v>298.61876000000007</v>
       </c>
       <c r="O22" s="119">
         <f t="shared" si="6"/>
-        <v>43.792449000000005</v>
+        <v>41.399419000000009</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="1"/>
-        <v>1795.4904090000002</v>
+        <v>1697.3761790000003</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -7776,23 +7776,23 @@
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>78.460000000000022</v>
+        <v>156.92000000000004</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>1435.8180000000002</v>
+        <v>1357.3580000000002</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>315.87996000000004</v>
+        <v>298.61876000000007</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>43.792449000000005</v>
+        <v>41.399419000000009</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>1795.4904090000002</v>
+        <v>1697.3761790000003</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -7863,7 +7863,7 @@
       <c r="O29" s="234"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>78.460000000000022</v>
+        <v>156.92000000000004</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7906,7 +7906,7 @@
       <c r="O31" s="234"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>1435.8180000000002</v>
+        <v>1357.3580000000002</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7931,7 +7931,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>315.87996000000004</v>
+        <v>298.61876000000007</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7953,7 +7953,7 @@
       <c r="O33" s="236"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>1751.6979600000002</v>
+        <v>1655.9767600000002</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>43.792449000000005</v>
+        <v>41.399419000000009</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -7988,7 +7988,7 @@
       <c r="O35" s="214"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>1795.4904090000002</v>
+        <v>1697.3761790000003</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -8068,7 +8068,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="10" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <pageSetup scale="10" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -8160,7 +8160,7 @@
       <c r="M4" s="239"/>
       <c r="N4" s="253">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="253"/>
       <c r="P4" s="253"/>
@@ -8188,7 +8188,7 @@
       <c r="M5" s="239"/>
       <c r="N5" s="253">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="240"/>
       <c r="P5" s="240"/>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
@@ -8548,8 +8548,8 @@
         <v>0</v>
       </c>
       <c r="J17" s="117"/>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="K17" s="104">
+        <f t="shared" ref="K17:K22" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
@@ -8608,7 +8608,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="117"/>
-      <c r="K18" s="1">
+      <c r="K18" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -8664,7 +8664,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="117"/>
-      <c r="K19" s="1">
+      <c r="K19" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -8720,7 +8720,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="117"/>
-      <c r="K20" s="1">
+      <c r="K20" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -8776,7 +8776,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="117"/>
-      <c r="K21" s="1">
+      <c r="K21" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -8832,12 +8832,12 @@
         <v>0</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L22" s="120">
-        <f>I22*5%</f>
+        <f>I22*10%</f>
         <v>0</v>
       </c>
       <c r="M22" s="118">
@@ -9381,7 +9381,7 @@
       <c r="M4" s="239"/>
       <c r="N4" s="253">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="253"/>
       <c r="P4" s="253"/>
@@ -9409,7 +9409,7 @@
       <c r="M5" s="239"/>
       <c r="N5" s="253">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="240"/>
       <c r="P5" s="240"/>
@@ -9710,7 +9710,7 @@
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
@@ -9769,8 +9769,8 @@
         <v>0</v>
       </c>
       <c r="J17" s="117"/>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="K17" s="104">
+        <f t="shared" ref="K17:K22" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
@@ -9829,7 +9829,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="117"/>
-      <c r="K18" s="1">
+      <c r="K18" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -9885,7 +9885,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="117"/>
-      <c r="K19" s="1">
+      <c r="K19" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -9941,7 +9941,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="117"/>
-      <c r="K20" s="1">
+      <c r="K20" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -9997,7 +9997,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="117"/>
-      <c r="K21" s="1">
+      <c r="K21" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -10053,12 +10053,12 @@
         <v>0</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L22" s="120">
-        <f>I22*5%</f>
+        <f>I22*10%</f>
         <v>0</v>
       </c>
       <c r="M22" s="118">
@@ -10599,7 +10599,7 @@
       <c r="M4" s="239"/>
       <c r="N4" s="253">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="253"/>
       <c r="P4" s="253"/>
@@ -10627,7 +10627,7 @@
       <c r="M5" s="239"/>
       <c r="N5" s="253">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="240"/>
       <c r="P5" s="240"/>
@@ -10928,7 +10928,7 @@
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
@@ -10987,8 +10987,8 @@
         <v>0</v>
       </c>
       <c r="J17" s="117"/>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="K17" s="104">
+        <f t="shared" ref="K17:K22" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
@@ -11047,7 +11047,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="117"/>
-      <c r="K18" s="1">
+      <c r="K18" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -11103,7 +11103,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="117"/>
-      <c r="K19" s="1">
+      <c r="K19" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -11159,7 +11159,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="117"/>
-      <c r="K20" s="1">
+      <c r="K20" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -11215,7 +11215,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="117"/>
-      <c r="K21" s="1">
+      <c r="K21" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -11271,12 +11271,12 @@
         <v>0</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L22" s="120">
-        <f>I22*5%</f>
+        <f>I22*10%</f>
         <v>0</v>
       </c>
       <c r="M22" s="118">
@@ -11816,7 +11816,7 @@
       <c r="M4" s="239"/>
       <c r="N4" s="253">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="253"/>
       <c r="P4" s="253"/>
@@ -11844,7 +11844,7 @@
       <c r="M5" s="239"/>
       <c r="N5" s="253">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="240"/>
       <c r="P5" s="240"/>
@@ -12145,7 +12145,7 @@
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
@@ -12204,8 +12204,8 @@
         <v>0</v>
       </c>
       <c r="J17" s="117"/>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="K17" s="104">
+        <f t="shared" ref="K17:K22" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
@@ -12264,7 +12264,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="117"/>
-      <c r="K18" s="1">
+      <c r="K18" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -12320,7 +12320,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="117"/>
-      <c r="K19" s="1">
+      <c r="K19" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -12376,7 +12376,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="117"/>
-      <c r="K20" s="1">
+      <c r="K20" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -12432,7 +12432,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="117"/>
-      <c r="K21" s="1">
+      <c r="K21" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -12488,12 +12488,12 @@
         <v>0</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L22" s="120">
-        <f>I22*5%</f>
+        <f>I22*10%</f>
         <v>0</v>
       </c>
       <c r="M22" s="118">
@@ -13033,7 +13033,7 @@
       <c r="M4" s="239"/>
       <c r="N4" s="253">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="253"/>
       <c r="P4" s="253"/>
@@ -13061,7 +13061,7 @@
       <c r="M5" s="239"/>
       <c r="N5" s="253">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="240"/>
       <c r="P5" s="240"/>
@@ -13362,7 +13362,7 @@
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
@@ -13421,8 +13421,8 @@
         <v>0</v>
       </c>
       <c r="J17" s="117"/>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="K17" s="104">
+        <f t="shared" ref="K17:K22" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
@@ -13481,7 +13481,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="117"/>
-      <c r="K18" s="1">
+      <c r="K18" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -13537,7 +13537,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="117"/>
-      <c r="K19" s="1">
+      <c r="K19" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -13593,7 +13593,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="117"/>
-      <c r="K20" s="1">
+      <c r="K20" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -13649,7 +13649,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="117"/>
-      <c r="K21" s="1">
+      <c r="K21" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -13705,12 +13705,12 @@
         <v>0</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L22" s="120">
-        <f>I22*5%</f>
+        <f>I22*10%</f>
         <v>0</v>
       </c>
       <c r="M22" s="118">
@@ -14250,7 +14250,7 @@
       <c r="M4" s="239"/>
       <c r="N4" s="253">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="253"/>
       <c r="P4" s="253"/>
@@ -14278,7 +14278,7 @@
       <c r="M5" s="239"/>
       <c r="N5" s="253">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="240"/>
       <c r="P5" s="240"/>
@@ -14579,7 +14579,7 @@
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
@@ -14638,8 +14638,8 @@
         <v>0</v>
       </c>
       <c r="J17" s="117"/>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="K17" s="104">
+        <f t="shared" ref="K17:K22" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
@@ -14698,7 +14698,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="117"/>
-      <c r="K18" s="1">
+      <c r="K18" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -14754,7 +14754,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="117"/>
-      <c r="K19" s="1">
+      <c r="K19" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -14810,7 +14810,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="117"/>
-      <c r="K20" s="1">
+      <c r="K20" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -14866,7 +14866,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="117"/>
-      <c r="K21" s="1">
+      <c r="K21" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -14922,12 +14922,12 @@
         <v>0</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L22" s="120">
-        <f>I22*5%</f>
+        <f>I22*10%</f>
         <v>0</v>
       </c>
       <c r="M22" s="118">
@@ -18217,7 +18217,7 @@
       <c r="M4" s="239"/>
       <c r="N4" s="253">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="253"/>
       <c r="P4" s="253"/>
@@ -18245,7 +18245,7 @@
       <c r="M5" s="239"/>
       <c r="N5" s="253">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="240"/>
       <c r="P5" s="240"/>
@@ -18546,7 +18546,7 @@
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
@@ -18605,8 +18605,8 @@
         <v>0</v>
       </c>
       <c r="J17" s="117"/>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="K17" s="104">
+        <f t="shared" ref="K17:K22" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
@@ -18665,7 +18665,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="117"/>
-      <c r="K18" s="1">
+      <c r="K18" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -18721,7 +18721,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="117"/>
-      <c r="K19" s="1">
+      <c r="K19" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -18777,7 +18777,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="117"/>
-      <c r="K20" s="1">
+      <c r="K20" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -18833,7 +18833,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="117"/>
-      <c r="K21" s="1">
+      <c r="K21" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -18889,12 +18889,12 @@
         <v>0</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L22" s="120">
-        <f>I22*5%</f>
+        <f>I22*10%</f>
         <v>0</v>
       </c>
       <c r="M22" s="118">
@@ -19434,7 +19434,7 @@
       <c r="M4" s="239"/>
       <c r="N4" s="253">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="253"/>
       <c r="P4" s="253"/>
@@ -19462,7 +19462,7 @@
       <c r="M5" s="239"/>
       <c r="N5" s="253">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="240"/>
       <c r="P5" s="240"/>
@@ -19763,7 +19763,7 @@
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
@@ -19822,8 +19822,8 @@
         <v>0</v>
       </c>
       <c r="J17" s="117"/>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="K17" s="104">
+        <f t="shared" ref="K17:K22" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
@@ -19882,7 +19882,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="117"/>
-      <c r="K18" s="1">
+      <c r="K18" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -19938,7 +19938,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="117"/>
-      <c r="K19" s="1">
+      <c r="K19" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -19994,7 +19994,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="117"/>
-      <c r="K20" s="1">
+      <c r="K20" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -20050,7 +20050,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="117"/>
-      <c r="K21" s="1">
+      <c r="K21" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -20106,12 +20106,12 @@
         <v>0</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L22" s="120">
-        <f>I22*5%</f>
+        <f>I22*10%</f>
         <v>0</v>
       </c>
       <c r="M22" s="118">
@@ -20651,7 +20651,7 @@
       <c r="M4" s="239"/>
       <c r="N4" s="253">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="253"/>
       <c r="P4" s="253"/>
@@ -20679,7 +20679,7 @@
       <c r="M5" s="239"/>
       <c r="N5" s="253">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="240"/>
       <c r="P5" s="240"/>
@@ -20980,7 +20980,7 @@
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
@@ -21039,8 +21039,8 @@
         <v>0</v>
       </c>
       <c r="J17" s="117"/>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="K17" s="104">
+        <f t="shared" ref="K17:K22" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
@@ -21099,7 +21099,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="117"/>
-      <c r="K18" s="1">
+      <c r="K18" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -21155,7 +21155,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="117"/>
-      <c r="K19" s="1">
+      <c r="K19" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -21211,7 +21211,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="117"/>
-      <c r="K20" s="1">
+      <c r="K20" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -21267,7 +21267,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="117"/>
-      <c r="K21" s="1">
+      <c r="K21" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -21323,12 +21323,12 @@
         <v>0</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L22" s="120">
-        <f>I22*5%</f>
+        <f>I22*10%</f>
         <v>0</v>
       </c>
       <c r="M22" s="118">
@@ -21868,7 +21868,7 @@
       <c r="M4" s="239"/>
       <c r="N4" s="253">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="253"/>
       <c r="P4" s="253"/>
@@ -21896,7 +21896,7 @@
       <c r="M5" s="239"/>
       <c r="N5" s="253">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="240"/>
       <c r="P5" s="240"/>
@@ -22197,7 +22197,7 @@
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
@@ -22256,8 +22256,8 @@
         <v>0</v>
       </c>
       <c r="J17" s="117"/>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="K17" s="104">
+        <f t="shared" ref="K17:K22" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
@@ -22316,7 +22316,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="117"/>
-      <c r="K18" s="1">
+      <c r="K18" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -22372,7 +22372,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="117"/>
-      <c r="K19" s="1">
+      <c r="K19" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -22428,7 +22428,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="117"/>
-      <c r="K20" s="1">
+      <c r="K20" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -22484,7 +22484,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="117"/>
-      <c r="K21" s="1">
+      <c r="K21" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -22540,12 +22540,12 @@
         <v>0</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L22" s="120">
-        <f>I22*5%</f>
+        <f>I22*10%</f>
         <v>0</v>
       </c>
       <c r="M22" s="118">
@@ -23090,7 +23090,7 @@
       <c r="M4" s="239"/>
       <c r="N4" s="253">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="253"/>
       <c r="P4" s="253"/>
@@ -23118,7 +23118,7 @@
       <c r="M5" s="239"/>
       <c r="N5" s="253">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="240"/>
       <c r="P5" s="240"/>
@@ -23382,7 +23382,7 @@
       </c>
       <c r="U15" s="164">
         <f>+'2'!P35</f>
-        <v>1760.4564498000002</v>
+        <v>1664.2566438000003</v>
       </c>
       <c r="XFD15" t="s">
         <v>81</v>
@@ -23456,7 +23456,7 @@
       </c>
       <c r="U16" s="164">
         <f>+'3'!P35</f>
-        <v>5038.0081170000003</v>
+        <v>4817.1188454000003</v>
       </c>
       <c r="XFD16" t="s">
         <v>82</v>
@@ -23530,7 +23530,7 @@
       </c>
       <c r="U17" s="164">
         <f>+'4'!P35</f>
-        <v>1795.4904090000002</v>
+        <v>1697.3761790000003</v>
       </c>
       <c r="XFD17" t="s">
         <v>83</v>
@@ -23603,7 +23603,7 @@
       </c>
       <c r="U18" s="164">
         <f>+'5'!P35</f>
-        <v>1795.4904090000002</v>
+        <v>1697.3761790000003</v>
       </c>
     </row>
     <row r="19" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
@@ -23645,7 +23645,7 @@
       </c>
       <c r="K19" s="172">
         <f>+'1'!K19+'2'!K19+'4'!K19+'3'!K19+'5'!K19+'6'!K19+'7'!K19+'8'!K19+'9'!K19+'10'!K19</f>
-        <v>101.69600000000001</v>
+        <v>203.39200000000002</v>
       </c>
       <c r="L19" s="175">
         <f>+'1'!L19+'2'!L19+'4'!L19+'3'!L19+'5'!L19+'6'!L19+'7'!L19+'8'!L19+'9'!L19+'10'!L19</f>
@@ -23653,19 +23653,19 @@
       </c>
       <c r="M19" s="118">
         <f t="shared" si="2"/>
-        <v>5244.6080000000002</v>
+        <v>5142.9120000000003</v>
       </c>
       <c r="N19" s="101">
         <f>+'1'!N19+'2'!N19+'4'!N19+'3'!N19+'5'!N19+'6'!N19+'7'!N19+'8'!N19+'9'!N19+'10'!N19</f>
-        <v>1153.81376</v>
+        <v>1131.44064</v>
       </c>
       <c r="O19" s="101">
         <f>+'1'!O19+'2'!O19+'4'!O19+'3'!O19+'5'!O19+'6'!O19+'7'!O19+'8'!O19+'9'!O19+'10'!O19</f>
-        <v>31.992108800000004</v>
+        <v>31.3717632</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="0"/>
-        <v>6430.4138688000003</v>
+        <v>6305.7244031999999</v>
       </c>
       <c r="T19" s="163" t="str">
         <f>+'6'!A5</f>
@@ -23673,7 +23673,7 @@
       </c>
       <c r="U19" s="164">
         <f>+'6'!P35</f>
-        <v>269.32356135000003</v>
+        <v>254.60642684999999</v>
       </c>
     </row>
     <row r="20" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
@@ -23743,7 +23743,7 @@
       </c>
       <c r="U20" s="164">
         <f>+'7'!P35</f>
-        <v>448.87260225000006</v>
+        <v>424.34404475000008</v>
       </c>
     </row>
     <row r="21" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
@@ -23813,7 +23813,7 @@
       </c>
       <c r="U21" s="164">
         <f>+'8'!P35</f>
-        <v>448.87260225000006</v>
+        <v>424.34404475000008</v>
       </c>
     </row>
     <row r="22" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
@@ -23859,23 +23859,23 @@
       </c>
       <c r="L22" s="175">
         <f>+'1'!L22+'2'!L22+'4'!L22+'3'!L22+'5'!L22+'6'!L22+'7'!L22+'8'!L22+'9'!L22+'10'!L22</f>
-        <v>619.83400000000017</v>
+        <v>1082.7480000000003</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="2"/>
-        <v>9828.6841999999997</v>
+        <v>9365.7702000000008</v>
       </c>
       <c r="N22" s="101">
         <f>+'1'!N22+'2'!N22+'4'!N22+'3'!N22+'5'!N22+'6'!N22+'7'!N22+'8'!N22+'9'!N22+'10'!N22</f>
-        <v>2162.3105240000004</v>
+        <v>2060.4694440000003</v>
       </c>
       <c r="O22" s="101">
         <f>+'1'!O22+'2'!O22+'4'!O22+'3'!O22+'5'!O22+'6'!O22+'7'!O22+'8'!O22+'9'!O22+'10'!O22</f>
-        <v>196.58741450000005</v>
+        <v>186.29738550000002</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="0"/>
-        <v>12187.5821385</v>
+        <v>11612.537029500001</v>
       </c>
       <c r="T22" s="163" t="str">
         <f>+'9'!A5</f>
@@ -23883,7 +23883,7 @@
       </c>
       <c r="U22" s="164">
         <f>+'9'!P35</f>
-        <v>448.87260225000006</v>
+        <v>424.34404475000008</v>
       </c>
     </row>
     <row r="23" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
@@ -23953,7 +23953,7 @@
       </c>
       <c r="U23" s="164">
         <f>+'10'!P35</f>
-        <v>1795.4904090000002</v>
+        <v>1697.3761790000003</v>
       </c>
     </row>
     <row r="24" spans="1:21 16384:16384" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
@@ -24056,27 +24056,27 @@
       </c>
       <c r="K25" s="178">
         <f t="shared" si="3"/>
-        <v>830.94480000000021</v>
+        <v>932.64080000000013</v>
       </c>
       <c r="L25" s="179">
         <f t="shared" si="3"/>
-        <v>1885.3860000000004</v>
+        <v>2348.3000000000002</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="3"/>
-        <v>23930.549200000001</v>
+        <v>23365.939200000001</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>5264.720824</v>
+        <v>5140.5066239999996</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>282.60879100000005</v>
+        <v>271.69841640000004</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>29477.878815000004</v>
+        <v>28778.144240400004</v>
       </c>
       <c r="T25" s="163" t="str">
         <f>+'12'!A5</f>
@@ -24316,7 +24316,7 @@
       </c>
       <c r="U34" s="165">
         <f>SUM(U14:U33)</f>
-        <v>29477.878815000015</v>
+        <v>28778.144240400001</v>
       </c>
     </row>
     <row r="35" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24370,7 +24370,7 @@
       <c r="O37" s="234"/>
       <c r="P37" s="153">
         <f>L25</f>
-        <v>1885.3860000000004</v>
+        <v>2348.3000000000002</v>
       </c>
     </row>
     <row r="38" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24391,7 +24391,7 @@
       <c r="O38" s="234"/>
       <c r="P38" s="154">
         <f>K25</f>
-        <v>830.94480000000021</v>
+        <v>932.64080000000013</v>
       </c>
     </row>
     <row r="39" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24413,7 +24413,7 @@
       <c r="O39" s="234"/>
       <c r="P39" s="153">
         <f>P36-P37-P38</f>
-        <v>23930.549200000005</v>
+        <v>23365.939200000004</v>
       </c>
     </row>
     <row r="40" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24438,7 +24438,7 @@
       </c>
       <c r="P40" s="153">
         <f>N25</f>
-        <v>5264.720824</v>
+        <v>5140.5066239999996</v>
       </c>
     </row>
     <row r="41" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24460,7 +24460,7 @@
       <c r="O41" s="236"/>
       <c r="P41" s="153">
         <f>P39+P40</f>
-        <v>29195.270024000005</v>
+        <v>28506.445824000002</v>
       </c>
     </row>
     <row r="42" spans="1:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24485,7 +24485,7 @@
       </c>
       <c r="P42" s="153">
         <f>O42*P41</f>
-        <v>729.88175060000015</v>
+        <v>712.66114560000005</v>
       </c>
     </row>
     <row r="43" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24495,7 +24495,7 @@
       <c r="O43" s="214"/>
       <c r="P43" s="160">
         <f>P41+P42</f>
-        <v>29925.151774600006</v>
+        <v>29219.106969600001</v>
       </c>
     </row>
     <row r="44" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24575,7 +24575,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="10" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <pageSetup scale="10" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
@@ -24675,7 +24675,7 @@
       <c r="M4" s="239"/>
       <c r="N4" s="253">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="253"/>
       <c r="P4" s="253"/>
@@ -24703,7 +24703,7 @@
       <c r="M5" s="239"/>
       <c r="N5" s="253">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="240"/>
       <c r="P5" s="240"/>
@@ -25130,7 +25130,7 @@
       </c>
       <c r="J17" s="117"/>
       <c r="K17" s="104">
-        <f t="shared" ref="K17:K21" si="4">I17*3.5%</f>
+        <f t="shared" ref="K17:K22" si="4">I17*3.5%</f>
         <v>73.447500000000005</v>
       </c>
       <c r="L17" s="105">
@@ -25534,8 +25534,8 @@
         <v>1569.2000000000003</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="4"/>
         <v>54.922000000000011</v>
       </c>
       <c r="L22" s="120">
@@ -26095,7 +26095,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="10" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <pageSetup scale="10" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -26187,7 +26187,7 @@
       <c r="M4" s="239"/>
       <c r="N4" s="253">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="253"/>
       <c r="P4" s="253"/>
@@ -26215,7 +26215,7 @@
       <c r="M5" s="239"/>
       <c r="N5" s="253">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="240"/>
       <c r="P5" s="240"/>
@@ -26516,7 +26516,7 @@
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
@@ -26575,8 +26575,8 @@
         <v>0</v>
       </c>
       <c r="J17" s="117"/>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="K17" s="104">
+        <f t="shared" ref="K17:K22" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
@@ -26635,7 +26635,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="117"/>
-      <c r="K18" s="1">
+      <c r="K18" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -26691,7 +26691,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="117"/>
-      <c r="K19" s="1">
+      <c r="K19" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -26747,7 +26747,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="117"/>
-      <c r="K20" s="1">
+      <c r="K20" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -26803,7 +26803,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="117"/>
-      <c r="K21" s="1">
+      <c r="K21" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -26861,29 +26861,29 @@
         <v>1569.2000000000003</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="3"/>
         <v>54.922000000000011</v>
       </c>
       <c r="L22" s="120">
-        <f>I22*5%</f>
-        <v>78.460000000000022</v>
+        <f>I22*10%</f>
+        <v>156.92000000000004</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="5"/>
-        <v>1435.8180000000002</v>
+        <v>1357.3580000000002</v>
       </c>
       <c r="N22" s="118">
         <f t="shared" si="0"/>
-        <v>315.87996000000004</v>
+        <v>298.61876000000007</v>
       </c>
       <c r="O22" s="119">
         <f t="shared" si="6"/>
-        <v>8.7584898000000013</v>
+        <v>8.2798838000000021</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="1"/>
-        <v>1760.4564498000002</v>
+        <v>1664.2566438000003</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -27026,23 +27026,23 @@
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>78.460000000000022</v>
+        <v>156.92000000000004</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>1435.8180000000002</v>
+        <v>1357.3580000000002</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>315.87996000000004</v>
+        <v>298.61876000000007</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>8.7584898000000013</v>
+        <v>8.2798838000000021</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>1760.4564498000002</v>
+        <v>1664.2566438000003</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -27113,7 +27113,7 @@
       <c r="O29" s="234"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>78.460000000000022</v>
+        <v>156.92000000000004</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27156,7 +27156,7 @@
       <c r="O31" s="234"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>1435.8180000000002</v>
+        <v>1357.3580000000002</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27181,7 +27181,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>315.87996000000004</v>
+        <v>298.61876000000007</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27203,7 +27203,7 @@
       <c r="O33" s="236"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>1751.6979600000002</v>
+        <v>1655.9767600000002</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -27228,7 +27228,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>8.7584898000000013</v>
+        <v>8.2798838000000021</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -27238,7 +27238,7 @@
       <c r="O35" s="214"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>1760.4564498000002</v>
+        <v>1664.2566438000003</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -27318,7 +27318,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="10" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <pageSetup scale="10" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -27410,7 +27410,7 @@
       <c r="M4" s="239"/>
       <c r="N4" s="253">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="253"/>
       <c r="P4" s="253"/>
@@ -27438,7 +27438,7 @@
       <c r="M5" s="239"/>
       <c r="N5" s="253">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="240"/>
       <c r="P5" s="240"/>
@@ -27739,7 +27739,7 @@
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
@@ -27798,8 +27798,8 @@
         <v>0</v>
       </c>
       <c r="J17" s="117"/>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="K17" s="104">
+        <f t="shared" ref="K17:K22" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
@@ -27858,7 +27858,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="117"/>
-      <c r="K18" s="1">
+      <c r="K18" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -27916,9 +27916,9 @@
         <v>2905.6</v>
       </c>
       <c r="J19" s="117"/>
-      <c r="K19" s="1">
+      <c r="K19" s="104">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>101.69600000000001</v>
       </c>
       <c r="L19" s="105">
         <f t="shared" si="4"/>
@@ -27926,19 +27926,19 @@
       </c>
       <c r="M19" s="118">
         <f t="shared" si="5"/>
-        <v>2673.152</v>
+        <v>2571.4560000000001</v>
       </c>
       <c r="N19" s="118">
         <f t="shared" si="0"/>
-        <v>588.09343999999999</v>
+        <v>565.72032000000002</v>
       </c>
       <c r="O19" s="119">
         <f t="shared" si="6"/>
-        <v>16.306227200000002</v>
+        <v>15.6858816</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="1"/>
-        <v>3277.5516672000003</v>
+        <v>3152.8622015999999</v>
       </c>
     </row>
     <row r="20" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -27972,7 +27972,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="117"/>
-      <c r="K20" s="1">
+      <c r="K20" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -28028,7 +28028,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="117"/>
-      <c r="K21" s="1">
+      <c r="K21" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -28086,29 +28086,29 @@
         <v>1569.2000000000003</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="3"/>
         <v>54.922000000000011</v>
       </c>
       <c r="L22" s="120">
-        <f>I22*5%</f>
-        <v>78.460000000000022</v>
+        <f>I22*10%</f>
+        <v>156.92000000000004</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="5"/>
-        <v>1435.8180000000002</v>
+        <v>1357.3580000000002</v>
       </c>
       <c r="N22" s="118">
         <f t="shared" si="0"/>
-        <v>315.87996000000004</v>
+        <v>298.61876000000007</v>
       </c>
       <c r="O22" s="119">
         <f t="shared" si="6"/>
-        <v>8.7584898000000013</v>
+        <v>8.2798838000000021</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="1"/>
-        <v>1760.4564498000002</v>
+        <v>1664.2566438000003</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -28247,27 +28247,27 @@
       <c r="J25" s="138"/>
       <c r="K25" s="139">
         <f t="shared" si="9"/>
-        <v>54.922000000000011</v>
+        <v>156.61800000000002</v>
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>310.90800000000002</v>
+        <v>389.36800000000005</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>4108.97</v>
+        <v>3928.8140000000003</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>903.97340000000008</v>
+        <v>864.33908000000008</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>25.064717000000002</v>
+        <v>23.965765400000002</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>5038.0081170000003</v>
+        <v>4817.1188454000003</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -28338,7 +28338,7 @@
       <c r="O29" s="234"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>310.90800000000002</v>
+        <v>389.36800000000005</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -28359,7 +28359,7 @@
       <c r="O30" s="234"/>
       <c r="P30" s="154">
         <f>K25</f>
-        <v>54.922000000000011</v>
+        <v>156.61800000000002</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -28381,7 +28381,7 @@
       <c r="O31" s="234"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>4108.97</v>
+        <v>3928.8140000000003</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -28406,7 +28406,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>903.97340000000008</v>
+        <v>864.33908000000008</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -28428,7 +28428,7 @@
       <c r="O33" s="236"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>5012.9434000000001</v>
+        <v>4793.15308</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -28453,7 +28453,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>25.064717000000002</v>
+        <v>23.965765400000002</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -28463,7 +28463,7 @@
       <c r="O35" s="214"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>5038.0081170000003</v>
+        <v>4817.1188454000003</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -28543,7 +28543,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="10" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <pageSetup scale="10" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -28634,7 +28634,7 @@
       <c r="M4" s="239"/>
       <c r="N4" s="253">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="253"/>
       <c r="P4" s="253"/>
@@ -28662,7 +28662,7 @@
       <c r="M5" s="239"/>
       <c r="N5" s="253">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="240"/>
       <c r="P5" s="240"/>
@@ -28963,7 +28963,7 @@
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
@@ -29022,8 +29022,8 @@
         <v>0</v>
       </c>
       <c r="J17" s="117"/>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="K17" s="104">
+        <f t="shared" ref="K17:K22" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
@@ -29082,7 +29082,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="117"/>
-      <c r="K18" s="1">
+      <c r="K18" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -29138,7 +29138,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="117"/>
-      <c r="K19" s="1">
+      <c r="K19" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -29194,7 +29194,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="117"/>
-      <c r="K20" s="1">
+      <c r="K20" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -29250,7 +29250,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="117"/>
-      <c r="K21" s="1">
+      <c r="K21" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -29308,29 +29308,29 @@
         <v>1569.2000000000003</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="3"/>
         <v>54.922000000000011</v>
       </c>
       <c r="L22" s="120">
-        <f>I22*5%</f>
-        <v>78.460000000000022</v>
+        <f>I22*10%</f>
+        <v>156.92000000000004</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="5"/>
-        <v>1435.8180000000002</v>
+        <v>1357.3580000000002</v>
       </c>
       <c r="N22" s="118">
         <f t="shared" si="0"/>
-        <v>315.87996000000004</v>
+        <v>298.61876000000007</v>
       </c>
       <c r="O22" s="119">
         <f t="shared" si="6"/>
-        <v>43.792449000000005</v>
+        <v>41.399419000000009</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="1"/>
-        <v>1795.4904090000002</v>
+        <v>1697.3761790000003</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" hidden="1" x14ac:dyDescent="0.35">
@@ -29473,23 +29473,23 @@
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>78.460000000000022</v>
+        <v>156.92000000000004</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>1435.8180000000002</v>
+        <v>1357.3580000000002</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>315.87996000000004</v>
+        <v>298.61876000000007</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>43.792449000000005</v>
+        <v>41.399419000000009</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>1795.4904090000002</v>
+        <v>1697.3761790000003</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -29560,7 +29560,7 @@
       <c r="O29" s="234"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>78.460000000000022</v>
+        <v>156.92000000000004</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29603,7 +29603,7 @@
       <c r="O31" s="234"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>1435.8180000000002</v>
+        <v>1357.3580000000002</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29628,7 +29628,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>315.87996000000004</v>
+        <v>298.61876000000007</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29650,7 +29650,7 @@
       <c r="O33" s="236"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>1751.6979600000002</v>
+        <v>1655.9767600000002</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -29675,7 +29675,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>43.792449000000005</v>
+        <v>41.399419000000009</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -29685,7 +29685,7 @@
       <c r="O35" s="214"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>1795.4904090000002</v>
+        <v>1697.3761790000003</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -29765,7 +29765,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="10" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <pageSetup scale="10" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -29857,7 +29857,7 @@
       <c r="M4" s="239"/>
       <c r="N4" s="253">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="253"/>
       <c r="P4" s="253"/>
@@ -29885,7 +29885,7 @@
       <c r="M5" s="239"/>
       <c r="N5" s="253">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="240"/>
       <c r="P5" s="240"/>
@@ -30186,7 +30186,7 @@
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
@@ -30245,8 +30245,8 @@
         <v>0</v>
       </c>
       <c r="J17" s="117"/>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="K17" s="104">
+        <f t="shared" ref="K17:K22" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
@@ -30305,7 +30305,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="117"/>
-      <c r="K18" s="1">
+      <c r="K18" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -30361,7 +30361,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="117"/>
-      <c r="K19" s="1">
+      <c r="K19" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -30417,7 +30417,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="117"/>
-      <c r="K20" s="1">
+      <c r="K20" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -30473,7 +30473,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="117"/>
-      <c r="K21" s="1">
+      <c r="K21" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -30531,29 +30531,29 @@
         <v>1569.2000000000003</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="3"/>
         <v>54.922000000000011</v>
       </c>
       <c r="L22" s="120">
-        <f>I22*5%</f>
-        <v>78.460000000000022</v>
+        <f>I22*10%</f>
+        <v>156.92000000000004</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="5"/>
-        <v>1435.8180000000002</v>
+        <v>1357.3580000000002</v>
       </c>
       <c r="N22" s="118">
         <f t="shared" si="0"/>
-        <v>315.87996000000004</v>
+        <v>298.61876000000007</v>
       </c>
       <c r="O22" s="119">
         <f t="shared" si="6"/>
-        <v>43.792449000000005</v>
+        <v>41.399419000000009</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="1"/>
-        <v>1795.4904090000002</v>
+        <v>1697.3761790000003</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -30696,23 +30696,23 @@
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>78.460000000000022</v>
+        <v>156.92000000000004</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>1435.8180000000002</v>
+        <v>1357.3580000000002</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>315.87996000000004</v>
+        <v>298.61876000000007</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>43.792449000000005</v>
+        <v>41.399419000000009</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>1795.4904090000002</v>
+        <v>1697.3761790000003</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -30783,7 +30783,7 @@
       <c r="O29" s="234"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>78.460000000000022</v>
+        <v>156.92000000000004</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -30826,7 +30826,7 @@
       <c r="O31" s="234"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>1435.8180000000002</v>
+        <v>1357.3580000000002</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -30851,7 +30851,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>315.87996000000004</v>
+        <v>298.61876000000007</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -30873,7 +30873,7 @@
       <c r="O33" s="236"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>1751.6979600000002</v>
+        <v>1655.9767600000002</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -30898,7 +30898,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>43.792449000000005</v>
+        <v>41.399419000000009</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -30908,7 +30908,7 @@
       <c r="O35" s="214"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>1795.4904090000002</v>
+        <v>1697.3761790000003</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -30988,7 +30988,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="10" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <pageSetup scale="10" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -31080,7 +31080,7 @@
       <c r="M4" s="239"/>
       <c r="N4" s="253">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="253"/>
       <c r="P4" s="253"/>
@@ -31108,7 +31108,7 @@
       <c r="M5" s="239"/>
       <c r="N5" s="253">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="240"/>
       <c r="P5" s="240"/>
@@ -31409,7 +31409,7 @@
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
@@ -31468,8 +31468,8 @@
         <v>0</v>
       </c>
       <c r="J17" s="117"/>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="K17" s="104">
+        <f t="shared" ref="K17:K22" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
@@ -31528,7 +31528,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="117"/>
-      <c r="K18" s="1">
+      <c r="K18" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -31584,7 +31584,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="117"/>
-      <c r="K19" s="1">
+      <c r="K19" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -31640,7 +31640,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="117"/>
-      <c r="K20" s="1">
+      <c r="K20" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -31696,7 +31696,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="117"/>
-      <c r="K21" s="1">
+      <c r="K21" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -31754,29 +31754,29 @@
         <v>235.38000000000002</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="3"/>
         <v>8.2383000000000024</v>
       </c>
       <c r="L22" s="120">
-        <f>I22*5%</f>
-        <v>11.769000000000002</v>
+        <f>I22*10%</f>
+        <v>23.538000000000004</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="5"/>
-        <v>215.37270000000001</v>
+        <v>203.6037</v>
       </c>
       <c r="N22" s="118">
         <f t="shared" si="0"/>
-        <v>47.381993999999999</v>
+        <v>44.792814</v>
       </c>
       <c r="O22" s="119">
         <f t="shared" si="6"/>
-        <v>6.5688673500000014</v>
+        <v>6.2099128500000003</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="1"/>
-        <v>269.32356135000003</v>
+        <v>254.60642684999999</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -31919,23 +31919,23 @@
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>11.769000000000002</v>
+        <v>23.538000000000004</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>215.37270000000001</v>
+        <v>203.6037</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>47.381993999999999</v>
+        <v>44.792814</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>6.5688673500000014</v>
+        <v>6.2099128500000003</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>269.32356135000003</v>
+        <v>254.60642684999999</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -32006,7 +32006,7 @@
       <c r="O29" s="234"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>11.769000000000002</v>
+        <v>23.538000000000004</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -32049,7 +32049,7 @@
       <c r="O31" s="234"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>215.37270000000001</v>
+        <v>203.6037</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>47.381993999999999</v>
+        <v>44.792814</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -32096,7 +32096,7 @@
       <c r="O33" s="236"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>262.75469400000003</v>
+        <v>248.396514</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -32121,7 +32121,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>6.5688673500000014</v>
+        <v>6.2099128500000003</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -32131,7 +32131,7 @@
       <c r="O35" s="214"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>269.32356135000003</v>
+        <v>254.60642684999999</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -32211,7 +32211,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="10" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <pageSetup scale="10" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
